--- a/Quotation_Tracker.xlsx
+++ b/Quotation_Tracker.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -865,6 +865,230 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Rajby Industries</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>procurement@rajby.com</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>PR-2026-101</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Safety Gloves Heavy Duty</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Pairs</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>19-Jun-2026</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>02:55 PM</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr"/>
+      <c r="N7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Hunar Foundation</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>admin@hunar.org</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>PR-HF-045</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>A4 Paper 80 GSM</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Reams</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>19-Jun-2026</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>02:55 PM</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Rajby Industries</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>procurement@rajby.com</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>PR-2026-101</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Safety Helmets Yellow</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Nos</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>19-Jun-2026</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>02:55 PM</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Al-Karam Textile</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>purchase@alkaram.com</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>PR-AK-009</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Industrial Lubricant Oil</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Ltrs</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19-Jun-2026</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>02:55 PM</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quotation_Tracker.xlsx
+++ b/Quotation_Tracker.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,11 +31,38 @@
       <sz val="11"/>
     </font>
     <font>
-      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002E7D32"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00F57F17"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C62828"/>
     </font>
   </fonts>
   <fills count="8">
@@ -53,20 +80,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FF4444"/>
+        <bgColor rgb="00FF4444"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD700"/>
-        <bgColor rgb="00FFD700"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DEEAF1"/>
-        <bgColor rgb="00DEEAF1"/>
+        <fgColor rgb="00E8F5E0"/>
+        <bgColor rgb="00E8F5E0"/>
       </patternFill>
     </fill>
     <fill>
@@ -77,8 +98,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF4444"/>
-        <bgColor rgb="00FF4444"/>
+        <fgColor rgb="00FFFDE7"/>
+        <bgColor rgb="00FFFDE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD700"/>
+        <bgColor rgb="00FFD700"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,58 +118,73 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color rgb="00000000"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color rgb="00000000"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color rgb="00000000"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color rgb="00000000"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00AAAAAA"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00AAAAAA"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00AAAAAA"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00AAAAAA"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -508,26 +550,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" customHeight="1">
+    <row r="1" ht="38" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sr#</t>
@@ -599,495 +641,416 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="6" t="n">
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Rajby Industries</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>procurement@rajby.com</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>PR-2026-001</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>Industrial Safety Gloves - Heavy Duty</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>Pairs</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="inlineStr"/>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>15-Jun-2026</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>02:53 PM</t>
-        </is>
-      </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Usama.Nadeem@rajby.com.pk</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical Tools</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Tool Box 3-Step (Metal) + Ring Spanner Set + Makute Screwdriver Set (100pcs) + Electrical Tools</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>11-Jun-2026</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>02:58 PM</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>OVERDUE</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>Reminder x2 received (12-Jun &amp; 19-Jun) — No quotation sent yet!</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Rajby Industries</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Usama.Nadeem@rajby.com.pk</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>PR# 928</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Wooden Patti 1 x 1 Inch x 10 Feet</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Feet</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>17-Jun-2026</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>02:40 PM</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>OVERDUE</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Reminder received 18-Jun — No quotation sent yet!</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Rajby Industries</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Usama.Nadeem@rajby.com.pk</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>PR# 23636</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>HP EliteBook 850 G5/G6 — Refurbished Core i5 8th Gen, 8GB RAM, 512GB SSD, 15.6" FHD, Backlit KB</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Nos</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>94,500</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>18-Jun-2026</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>03:36 PM</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>18-Jun-2026 04:22 PM</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>Quoted @ Rs 94,500</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Rajby Industries</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Shoaib.Shahid@rajby.com.pk</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Finishing WAT Dispenser — 3A-WAT202 (Automatic Tape Cutter Machine)</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Nos</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>19-Jun-2026</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>11:52 AM</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr"/>
-      <c r="M2" s="6" t="inlineStr">
-        <is>
-          <t>Urgent requirement</t>
-        </is>
-      </c>
-      <c r="N2" s="6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>Video &amp; pictures attached by client</t>
+        </is>
+      </c>
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Rajby Industries</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>procurement@rajby.com</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>PR-2026-001</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Safety Helmets - Yellow</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>M.anas@rajby.com.pk</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>PR-22816</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Stitching Machine FEEDO — JUKI MS 1261 [FOA] Misc. Regulator Controller (Meter) Complete Set</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>19-Jun-2026</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>09:39 AM</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr"/>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>Brand mention required. Letterhead + all taxes inclusive</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Hunar Foundation</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>wajeeha.nasir@hunarfoundation.org</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>RFQ: Fans</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Fans (Various Sizes) — Delivery: SZAKATI Institute, Orangi Town</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Nos</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>19-Jun-2026</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>02:53 PM</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>Added to same PR - follow up call</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Hunar Foundation</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>admin@hunarfoundation.org</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>PR-HF-045</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>A4 Paper Ream 80 GSM</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Reams</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>02:53 PM</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Monthly stationery requirement</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>ABC Textiles</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>purchase@abctextiles.com</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>PR-ABC-022</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Industrial Lubricant Oil</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Litres</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>02:53 PM</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="K6" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>11:10 AM</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>Sent</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>19-Jun-2026 02:53 PM</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Quotation sent via email - awaiting PO</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Rajby Industries</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>procurement@rajby.com</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>PR-2026-101</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Safety Gloves Heavy Duty</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Pairs</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>02:55 PM</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Hunar Foundation</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>admin@hunar.org</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>PR-HF-045</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>A4 Paper 80 GSM</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Reams</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>02:55 PM</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Rajby Industries</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>procurement@rajby.com</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>PR-2026-101</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Safety Helmets Yellow</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Nos</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>02:55 PM</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Al-Karam Textile</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>purchase@alkaram.com</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>PR-AK-009</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Industrial Lubricant Oil</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Ltrs</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19-Jun-2026</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>02:55 PM</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>19-Jun-2026 04:27 PM</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>QT-001073 sent. Client asked for fan pictures — FOLLOW UP NEEDED</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Total Queries: 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>✅ Sent: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>⏳ Pending: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>🚨 Overdue: 2</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
